--- a/output/laminas_comunales/comunal_i_ingr_median_a_2020_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2020_los_rios.xlsx
@@ -636,7 +636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -645,50 +645,33 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Corral</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>539740</v>
+          <t>La Unión</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Futrono</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>484142</v>
+          <t>Los Lagos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>La Unión</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>553890</v>
+          <t>Máfil</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>473000</v>
+          <t>Paillaco</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -697,28 +680,19 @@
           <t>Lanco</t>
         </is>
       </c>
-      <c r="B6">
-        <v>536331</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>515551.5</v>
+          <t>Panguipulli</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Máfil</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>530041.5</v>
+          <t>Río Bueno</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -727,48 +701,33 @@
           <t>Mariquina</t>
         </is>
       </c>
-      <c r="B9">
-        <v>550000.5</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paillaco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>509786.5</v>
+          <t>Corral</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>490940</v>
+          <t>Valdivia</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>505662.5</v>
+          <t>Lago Ranco</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>628750</v>
+          <t>Futrono</t>
+        </is>
       </c>
     </row>
   </sheetData>
